--- a/docs/测试用例/SynaRoute测试用例-1-通用（先测这个）.xlsx
+++ b/docs/测试用例/SynaRoute测试用例-1-通用（先测这个）.xlsx
@@ -11,7 +11,7 @@
     <sheet name="用例" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'用例'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'用例'!$A$1:$J$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -165,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -198,6 +204,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,7 +589,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>版本 0.1.8    用例 33 条（其中 P0 必测 10 条）</t>
+          <t>版本 0.1.9    用例 39 条（其中 P0 必测 11 条）</t>
         </is>
       </c>
     </row>
@@ -747,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2314,15 +2323,287 @@
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="9" t="n"/>
     </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>v0.1.9 本轮修复（真机测出，重点回归）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>G-34</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>故障转移措辞不再张口就说「限流」</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>配 2 条 Key，其中第 1 条 base_url 指向一个必然 502/503 的地址（或密钥填错造 401）</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>发一次请求触发故障转移 → 看运行日志里那条 failover 记录的措辞</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>措辞须与真实状态码对应：401/403=「鉴权失败」、400=「请求被拒（非 Key 问题）」、502~504=「上游故障/无可用渠道」。**只有真的 429 才允许出现「限流」二字**</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>运行日志 failover 行 + 对照该行括号里的 HTTP 状态码</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>G-35</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>下游不传模型名时不再全池 400</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>任一分类配好 ≥2 条 Key，并给主 Key 填上「默认兜底模型」</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>用不带 model 字段的请求打代理：curl -X POST http://127.0.0.1:&lt;端口&gt;/v1/messages -H "content-type: application/json" -d '{"messages":[{"role":"user","content":"hi"}],"max_tokens":16}'</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>请求应成功（代理自动用兜底模型），**不应**出现「model is required」/「Model name not specified」，也不应出现「全部 Key 失败」</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>curl 返回体 + 运行日志里实际发往上游的 model 字段</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>G-36</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>拉取模型失败给出可行动提示</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>新建一条 Key，base_url 填一个会返回网页的地址（如 https://www.baidu.com）</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>点「拉取模型」</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>提示应说明「返回的是网页而不是 JSON」并指向检查 Base URL；**不得**再出现 expected value at line 1 column 1 这类术语。换一个连不上的地址（如 https://nonexistent.invalid）→ 应说「连不上」并提示检查域名/代理</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>错误提示原文</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>G-37</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>1M 上下文按窗口自动启用</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>一条 Anthropic 协议的 Key，其模型的上下文窗口填 1000000</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>在模型列表里看该行；再发一次请求并查看发往上游的请求头</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>该行出现「1M」徽标；转发时请求头 anthropic-beta 含 context-1m-2025-08-07，且客户端原有的 claude-code-20250219 等特性**仍在**（是追加不是覆盖）</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>UI 徽标 + 运行日志的链路快照（需开启「调用模型日志」）</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>G-38</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>窗口不足 1M 时不得谎称支持</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>把上一条的窗口改成 200000</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>重新发一次请求</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>anthropic-beta 里**不应**出现 context-1m-2025-08-07（无依据不断言）；模型行也不该有 1M 徽标</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>链路快照里的请求头</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>G-39</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.9</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>图标已回退为原图标</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>安装 v0.1.9 正式包</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>看任务栏 / 窗口标题栏 / 托盘 / 开始菜单</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>均为**换图标之前**的原图标</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>肉眼</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J37"/>
-  <mergeCells count="3">
+  <autoFilter ref="A1:J44"/>
+  <mergeCells count="4">
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"通过,失败,阻塞,跳过"</formula1>
     </dataValidation>
   </dataValidations>
